--- a/tasks/HR_Troutly_T1_august_operating_review/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T1_august_operating_review/05_rubric_import.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_dc228e8bba9d423fbe9f3dd35862f658", "transformations": []}]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Executive/Board/2026-06-20_Board_Minutes.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Executive/Board/2026-06-20_Board_Minutes.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -708,7 +708,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/Hiring_Plan_2026_FINAL.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Hiring_Plan_2026_FINAL.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/Hiring_Plan_2026_FINAL.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Hiring_Plan_2026_FINAL.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Finance/2026-08-06_Fully_Loaded_Cost_Memo.docx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/Offers/2026-08-20_Offer_Acceptance_ATS-4471.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Finance/2026-08-06_Fully_Loaded_Cost_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/Offers/2026-07-09_Start_Date_Thread_TRT-0153.eml", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/People/Onboarding/2026-07-22_IT_Ticket_TRT-0153.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/Offers/2026-07-09_Start_Date_Thread_TRT-0153.eml", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Onboarding/2026-07-22_IT_Ticket_TRT-0153.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Executive/Board/2026-06-20_Board_Minutes.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/Hiring_Plan_2026_FINAL.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Executive/Board/2026-06-20_Board_Minutes.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Hiring_Plan_2026_FINAL.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/2026-06-20_Hiring_Plan_Board_Approved.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_dc228e8bba9d423fbe9f3dd35862f658", "transformations": []}]</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Wiki/People_Metrics.md", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/People_Metrics.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/People/Onboarding/2026-07-22_IT_Ticket_TRT-0153.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Onboarding/2026-07-22_IT_Ticket_TRT-0153.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/People/Separations/2026-05-29_Resignation_TRT-0064.eml", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/People/Separations/2026-05-29_Resignation_TRT-0064.eml", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Wiki/People_Metrics.md", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Finance/2026-08-06_Fully_Loaded_Cost_Memo.docx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/People_Metrics.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Finance/2026-08-06_Fully_Loaded_Cost_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Org/2026-08-24_Org_Chart.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/Wiki/People_Metrics.md", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/Wiki/People_Metrics.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_dc228e8bba9d423fbe9f3dd35862f658", "transformations": []}]</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "SNAPSHOT_ID_NOT_YET_READ", "transformations": []}]</t>
+          <t>[{"name": "filesystem/operating_review_request.pdf", "index": null, "source": "task", "snapshotId": "snap_dc228e8bba9d423fbe9f3dd35862f658", "transformations": []}, {"name": "filesystem/Recruiting/ATS_Requisition_Export_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
